--- a/tests/fixtures/sample_season_workbook.xlsx
+++ b/tests/fixtures/sample_season_workbook.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M2" s="1" t="n">
@@ -631,7 +631,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>WRA5749J/WRA5925F</t>
+          <t>JSI4708L/SMM8968H</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Łukasz</t>
+          <t>Jani</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M3" s="1" t="n">
@@ -751,7 +751,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>WR367HW/WPYTP71</t>
+          <t>BM819DS/YUEVV45</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Mikołaj</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Black Fox</t>
+          <t>TOLEBAVAT REBAL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>WRA6405K/WRA6065K</t>
+          <t>YCB7683F/ENK6596V</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Philip</t>
+          <t>Mareki</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M5" s="1" t="n">
@@ -982,7 +982,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adami</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M6" s="1" t="n">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>RJA0349C/WPYRP70</t>
+          <t>ABV9024D/FARJM83</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Mikołaj</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M2" s="1" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>WR433GX/WR0629Y</t>
+          <t>QT523RK/KG3126I</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Karol</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M3" s="1" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>WRA89914/WRA9377J</t>
+          <t>JHH65532/LSL3043Z</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Ilona</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Black Fox</t>
+          <t>TOLEBAVAT REBAL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>WGR24990/WGR6UY</t>
+          <t>QWW83681/GIL1HT</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Annai</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M5" s="1" t="n">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>WX 12345/WPI19693</t>
+          <t>WX 12345/JXC36691</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>trailer WPI19693 with another truck</t>
+          <t>trailer JXC36691 with another truck</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M6" s="1" t="n">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>LLU5685E/LLU63516</t>
+          <t>MLB7342B/UCW84682</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Ilona</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M2" s="1" t="n">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>PY5655C/PY5595Y</t>
+          <t>VI1848M/JX1863B</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M3" s="1" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>PY70711/PO5XY55</t>
+          <t>NO30608/TT2ZV17</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Black Fox</t>
+          <t>TOLEBAVAT REBAL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>PY9890E/WGM7700R</t>
+          <t>RM8536M/ZUE2056G</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M5" s="1" t="n">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>PY6222L/PGN6FC8</t>
+          <t>XD0224P/LTA8IL8</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M2" s="1" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>W8LEON2/WPI19693</t>
+          <t>V0BOVU5/JXC36691</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M3" s="1" t="n">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>WGM4307U/WGM0993R</t>
+          <t>WVA9930P/BQR5495F</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Black Fox</t>
+          <t>TOLEBAVAT REBAL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M5" s="1" t="n">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M2" s="1" t="n">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Grójecki Owoc</t>
+          <t>Pavamane Owoc</t>
         </is>
       </c>
       <c r="M3" s="1" t="n">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Black Fox</t>
+          <t>TOLEBAVAT REBAL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
